--- a/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa marche avec maman. Elles vont à la boulangerie. Le pain sent le beurre chaud. Elles arrivent au bord. Léa s'arrête. S'arrêter, c'est le geste. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman s'arrête aussi. Maman dit : on s'arrête. Pieds au bord. Sur le trottoir. Léa sent le vent sur les joues. Elle attend avec maman. Les pieds restent calmes. Plus tard, elles ont le pain. Le sac est tiède. Elles vont au jardin public. Un autre bord arrive. Léa se souvient. Elle s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman dit : tu as repris le geste. Même règle, autre chemin. Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.</t>
+          <t>Léa marche avec maman. Elles vont à la boulangerie. Le pain sent le beurre chaud. Elles arrivent au bord. Léa s'arrête. S'arrêter, c'est le geste. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman s'arrête aussi. On s'arrête. Pieds au bord. Sur le trottoir. Léa sent le vent sur les joues. Elle attend avec maman. Les pieds restent calmes. Plus tard, elles ont le pain. Le sac est tiède. Elles vont au jardin public. Un autre bord arrive. Léa se souvient. Elle s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir. Tu as repris le geste. Même règle, autre chemin. Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa marche avec maman. Elles vont à la boulangerie. Le pain sent le beurre chaud. Elles arrivent au bord. Léa s'arrête. S'arrêter, c'est le geste. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman s'arrête aussi.
+maman|On s'arrête. Pieds au bord. Sur le trottoir.
+narrateur|Léa sent le vent sur les joues. Elle attend avec maman. Les pieds restent calmes. Plus tard, elles ont le pain. Le sac est tiède. Elles vont au jardin public. Un autre bord arrive. Léa se souvient. Elle s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir.
+maman|Tu as repris le geste. Même règle, autre chemin.
+narrateur|Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léa arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête au bord. Les pieds sont sur le trottoir. Elle a repris le geste. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa tient le sac de pain. Maman serre sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Léa arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Léa s'arrête au bord. Les pieds sont sur le trottoir. Elle a repris le geste. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1855,7 @@
           <t>narrateur|Léa tient le sac de pain. Maman serre sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léa s'arrête deux fois</t>
+          <t>Le pain tiède de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La vitre est buée. Sarah et maman vont chercher le pain. Au premier bord, Sarah s'arrête. Pieds au bord. Plus tard, vers le jardin, elle s'arrête encore. Le sac est tiède.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa marche avec maman. Elles vont à la boulangerie. Le pain sent le beurre chaud. Elles arrivent au bord. Léa s'arrête. S'arrêter, c'est le geste. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman s'arrête aussi. On s'arrête. Pieds au bord. Sur le trottoir. Léa sent le vent sur les joues. Elle attend avec maman. Les pieds restent calmes. Plus tard, elles ont le pain. Le sac est tiède. Elles vont au jardin public. Un autre bord arrive. Léa se souvient. Elle s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir. Tu as repris le geste. Même règle, autre chemin. Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.</t>
+          <t>La vitre de la cuisine est toute buée. Un petit doigt y dessine un rond. Dehors, le village sent le beurre chaud. Un sac jaune attend sur la chaise. Le tissu du sac est un peu rêche. Les chaussettes de Sarah sèchent près du radiateur. Elles sont épaisses, toutes chaudes. Sarah vit ici, avec maman. Maman, la vitre est toute douce ! Oui. Le four de la boulangerie est allumé. Tu mets tes chaussettes chaudes ? En ce moment, Sarah s'assoit près du radiateur. Elle enfile les chaussettes épaisses. Puis les petites chaussures brunes. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le sac jaune. Maman ouvre la porte. L'air sent le beurre et le pain. Une feuille colle au bas de la porte. Ça sent trop bon ! Oui. On marche sur le trottoir. Sarah donne la main à maman. Le sac jaune tape doucement contre la jambe. Elles passent devant une fenêtre orange. Le pain est tout proche maintenant. Le bord du trottoir arrive, gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Sarah s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Sarah. Le beurre sent encore plus fort. Bravo, Sarah. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,53 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa marche avec maman. Elles vont à la boulangerie. Le pain sent le beurre chaud. Elles arrivent au bord. Léa s'arrête. S'arrêter, c'est le geste. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman s'arrête aussi.
-maman|On s'arrête. Pieds au bord. Sur le trottoir.
-narrateur|Léa sent le vent sur les joues. Elle attend avec maman. Les pieds restent calmes. Plus tard, elles ont le pain. Le sac est tiède. Elles vont au jardin public. Un autre bord arrive. Léa se souvient. Elle s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir.
-maman|Tu as repris le geste. Même règle, autre chemin.
-narrateur|Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.</t>
+          <t>narrateur|La vitre de la cuisine est toute buée.
+narrateur|Un petit doigt y dessine un rond.
+narrateur|Dehors, le village sent le beurre chaud.
+narrateur|Un sac jaune attend sur la chaise.
+narrateur|Le tissu du sac est un peu rêche.
+narrateur|Les chaussettes de Sarah sèchent près du radiateur.
+narrateur|Elles sont épaisses, toutes chaudes.
+narrateur|Sarah vit ici, avec maman.
+enfant-f|Maman, la vitre est toute douce !
+maman|Oui.
+maman|Le four de la boulangerie est allumé.
+maman|Tu mets tes chaussettes chaudes ?
+narrateur|En ce moment, Sarah s'assoit près du radiateur.
+narrateur|Elle enfile les chaussettes épaisses.
+narrateur|Puis les petites chaussures brunes.
+maman|Tu as fini tes chaussures ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|On prend le sac jaune.
+narrateur|Maman ouvre la porte.
+narrateur|L'air sent le beurre et le pain.
+narrateur|Une feuille colle au bas de la porte.
+enfant-f|Ça sent trop bon !
+maman|Oui.
+maman|On marche sur le trottoir.
+narrateur|Sarah donne la main à maman.
+narrateur|Le sac jaune tape doucement contre la jambe.
+narrateur|Elles passent devant une fenêtre orange.
+narrateur|Le pain est tout proche maintenant.
+narrateur|Le bord du trottoir arrive, gris et net.
+maman|On va s'arrêter.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+narrateur|Sarah s'arrête.
+narrateur|Ses pieds sont au bord.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+enfant-f|Je m'arrête.
+maman|Oui.
+maman|On attend avec maman.
+maman|Tes pieds sont calmes ?
+enfant-f|Oui.
+narrateur|Le vent touche les joues de Sarah.
+narrateur|Le beurre sent encore plus fort.
+maman|Bravo, Sarah.
+maman|Tu as fait du bon travail.
+narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1344,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léa arrive au bord. Que fait-elle ?</t>
+          <t>Sarah arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léa arrive au bord. Que fait-elle ?</t>
+          <t>narrateur|Sarah arrive au bord.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa s'arrête au bord. Les pieds sont sur le trottoir. Elle a repris le geste. Maman est là.</t>
+          <t>Sarah s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Sarah. On attend avec maman. La main de maman est chaude. Le sac jaune est un peu rêche. Le vent glisse encore sur les joues.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1735,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa s'arrête au bord. Les pieds sont sur le trottoir. Elle a repris le geste. Maman est là.</t>
+          <t>narrateur|Sarah s'arrête au bord.
+narrateur|Les pieds sont sur le trottoir.
+narrateur|Les pieds restent au bord.
+maman|Tu t'arrêtes au trottoir ?
+enfant-f|Oui.
+enfant-f|Je m'arrête.
+maman|Bravo, Sarah.
+maman|On attend avec maman.
+narrateur|La main de maman est chaude.
+narrateur|Le sac jaune est un peu rêche.
+narrateur|Le vent glisse encore sur les joues.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léa tient le sac de pain. Maman serre sa main.</t>
+          <t>On y va ensemble ? Oui, maman. Elles marchent avec l'adulte. La clochette de la boulangerie fait ding. Le pain est tiède dans le sac jaune. Il est chaud ! Oui. On va au jardin, maintenant. Plus loin, un autre bord arrive. Sarah se souvient du premier bord. On va s'arrêter ? Oui. Pieds au bord. Sur le trottoir. Sarah s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir. Tu as repris le même arrêt ? Oui. Bravo. Même règle, autre chemin. Le sac tiède pèse un peu. Le jardin sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1917,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léa tient le sac de pain. Maman serre sa main.</t>
+          <t>maman|On y va ensemble ?
+enfant-f|Oui, maman.
+narrateur|Elles marchent avec l'adulte.
+narrateur|La clochette de la boulangerie fait ding.
+narrateur|Le pain est tiède dans le sac jaune.
+enfant-f|Il est chaud !
+maman|Oui.
+maman|On va au jardin, maintenant.
+narrateur|Plus loin, un autre bord arrive.
+narrateur|Sarah se souvient du premier bord.
+enfant-f|On va s'arrêter ?
+maman|Oui.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+narrateur|Sarah s'arrête encore.
+narrateur|Les pieds restent au bord.
+narrateur|Les pieds sont sur le trottoir.
+maman|Tu as repris le même arrêt ?
+enfant-f|Oui.
+maman|Bravo.
+maman|Même règle, autre chemin.
+narrateur|Le sac tiède pèse un peu.
+narrateur|Le jardin sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1967,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Je me suis arrêtée deux fois. Pieds au bord. Sur le trottoir. Bravo, Sarah. Le pain tiède reste dans le sac jaune. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2107,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Je me suis arrêtée deux fois.
+maman|Pieds au bord.
+maman|Sur le trottoir.
+maman|Bravo, Sarah.
+narrateur|Le pain tiède reste dans le sac jaune.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2172,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine est toute buée. Un petit doigt y dessine un rond. Dehors, le village sent le beurre chaud. Un sac jaune attend sur la chaise. Le tissu du sac est un peu rêche. Les chaussettes de Sarah sèchent près du radiateur. Elles sont épaisses, toutes chaudes. Sarah vit ici, avec maman. Maman, la vitre est toute douce ! Oui. Le four de la boulangerie est allumé. Tu mets tes chaussettes chaudes ? En ce moment, Sarah s'assoit près du radiateur. Elle enfile les chaussettes épaisses. Puis les petites chaussures brunes. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le sac jaune. Maman ouvre la porte. L'air sent le beurre et le pain. Une feuille colle au bas de la porte. Ça sent trop bon ! Oui. On marche sur le trottoir. Sarah donne la main à maman. Le sac jaune tape doucement contre la jambe. Elles passent devant une fenêtre orange. Le pain est tout proche maintenant. Le bord du trottoir arrive, gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Sarah s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Sarah. Le beurre sent encore plus fort. Bravo, Sarah. Tu as fait du bon travail. Les pieds restent au bord du trottoir.</t>
+          <t>La vitre de la cuisine est toute buée. Un petit doigt y dessine un rond. Dehors, le village sent le beurre chaud. Un sac jaune attend sur la chaise. Le tissu du sac est un peu rêche. Les chaussettes de Sarah sèchent près du radiateur. Elles sont épaisses, toutes chaudes. Sarah vit ici, avec maman. Maman, la vitre est toute douce ! Oui. Le four de la boulangerie est allumé. Tu mets tes chaussettes chaudes ? En ce moment, Sarah s'assoit près du radiateur. Elle enfile les chaussettes épaisses. Puis les petites chaussures brunes. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le sac jaune. Maman ouvre la porte. L'air sent le beurre et le pain. Une feuille colle au bas de la porte. Ça sent trop bon ! Oui. On marche sur le trottoir. Sarah donne la main à maman. Le sac jaune tape doucement contre la jambe. Elles passent devant une fenêtre orange. Le pain est tout proche maintenant. Le bord du trottoir arrive, gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Sarah s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Sarah. Le beurre sent encore plus fort. Bravo, Sarah. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léa marche avec maman. Elles vont à la boulangerie. Le pain sent le beurre chaud. Elles arrivent au bord. Léa s'arrête. S'arrêter, c'est le geste. Les pieds restent au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Maman s'arrête aussi. Maman dit : on s'arrête. Pieds au bord. Sur le trottoir. Léa sent le vent sur les joues. Elle attend avec maman. Les pieds restent calmes. Plus tard, elles ont le pain. Le sac est tiède. Elles vont au jardin public. Un autre bord arrive. Léa se souvient. Elle s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir. Maman dit : tu as repris le geste. Même règle, autre chemin. Léa donne la main. Elles attendent. Les pieds restent au bord du trottoir.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine est toute buée. Un petit doigt y dessine un rond. Dehors, le village sent le beurre chaud. Un sac jaune attend sur la chaise. Le tissu du sac est un peu rêche. Les chaussettes de Sarah sèchent près du radiateur. Elles sont épaisses, toutes chaudes. Sarah vit ici, avec maman. Maman, la vitre est toute douce ! Oui. Le four de la boulangerie est allumé. Tu mets tes chaussettes chaudes ? En ce moment, Sarah s'assoit près du radiateur. Elle enfile les chaussettes épaisses. Puis les petites chaussures brunes. Tu as fini tes chaussures ? Oui, maman. Bravo. On prend le sac jaune. Maman ouvre la porte. L'air sent le beurre et le pain. Une feuille colle au bas de la porte. Ça sent trop bon ! Oui. On marche sur le trottoir. Sarah donne la main à maman. Le sac jaune tape doucement contre la jambe. Elles passent devant une fenêtre orange. Le pain est tout proche maintenant. Le bord du trottoir arrive, gris et net. On va s'arrêter. Pieds au bord. Sur le trottoir. Sarah s'arrête. Ses pieds sont au bord. Les pieds restent au bord. Les pieds sont sur le trottoir. Je m'arrête. Oui. On attend avec maman. Tes pieds sont calmes ? Oui. Le vent touche les joues de Sarah. Le beurre sent encore plus fort. Bravo, Sarah. Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1369,11 +1369,9 @@
 narrateur|Le vent touche les joues de Sarah.
 narrateur|Le beurre sent encore plus fort.
 maman|Bravo, Sarah.
-maman|Tu as fait du bon travail.
 narrateur|Les pieds restent au bord du trottoir.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1403,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Léa arrive au bord. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah arrive au bord. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1560,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1589,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Léa s'arrête au bord. Les pieds sont sur le &lt;emphasis level="moderate"&gt;trottoir&lt;/emphasis&gt;. Elle a repris le geste. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah s'arrête au bord. Les pieds sont sur le trottoir. Les pieds restent au bord. Tu t'arrêtes au trottoir ? Oui. Je m'arrête. Bravo, Sarah. On attend avec maman. La main de maman est chaude. Le sac jaune est un peu rêche. Le vent glisse encore sur les joues.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,7 +1745,6 @@
 narrateur|Le vent glisse encore sur les joues.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1778,7 +1774,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Léa tient le sac de pain. Maman serre sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On y va ensemble ? Oui, maman. Elles marchent avec l'adulte. La clochette de la boulangerie fait ding. Le pain est tiède dans le sac jaune. Il est chaud ! Oui. On va au jardin, maintenant. Plus loin, un autre bord arrive. Sarah se souvient du premier bord. On va s'arrêter ? Oui. Pieds au bord. Sur le trottoir. Sarah s'arrête encore. Les pieds restent au bord. Les pieds sont sur le trottoir. Tu as repris le même arrêt ? Oui. Bravo. Même règle, autre chemin. Le sac tiède pèse un peu. Le jardin sent l'herbe coupée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1942,7 +1938,6 @@
 narrateur|Le jardin sent l'herbe coupée.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1967,12 +1962,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Je me suis arrêtée deux fois. Pieds au bord. Sur le trottoir. Bravo, Sarah. Le pain tiède reste dans le sac jaune. L'histoire est finie.</t>
+          <t>Je me suis arrêtée deux fois. Pieds au bord. Sur le trottoir. Bravo, Sarah. Le pain tiède reste dans le sac jaune.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Je me suis arrêtée deux fois. Pieds au bord. Sur le trottoir. Bravo, Sarah. Le pain tiède reste dans le sac jaune.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2111,11 +2106,9 @@
 maman|Pieds au bord.
 maman|Sur le trottoir.
 maman|Bravo, Sarah.
-narrateur|Le pain tiède reste dans le sac jaune.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le pain tiède reste dans le sac jaune.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2134,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2179,6 +2172,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
+++ b/stories/arbres/ATOM-SEC.RUE.001-02.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trajet vers la boulangerie puis le jardin</t>
+          <t>cuisine embuée, trottoir vers la boulangerie, puis vers le jardin public</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
